--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.1401</v>
+        <v>16.98394</v>
       </c>
       <c r="D2" t="n">
-        <v>16.65414</v>
+        <v>16.79486</v>
       </c>
       <c r="E2" t="n">
-        <v>16.56434</v>
+        <v>16.87318</v>
       </c>
       <c r="F2" t="n">
-        <v>43.45323</v>
+        <v>42.42362</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05143</v>
+        <v>0.05137</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85789</v>
+        <v>1.85956</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.69492</v>
+        <v>17.07113</v>
       </c>
       <c r="D3" t="n">
-        <v>16.77012</v>
+        <v>16.81502</v>
       </c>
       <c r="E3" t="n">
-        <v>16.61028</v>
+        <v>16.95511</v>
       </c>
       <c r="F3" t="n">
-        <v>42.49713</v>
+        <v>43.10376</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05137</v>
+        <v>0.05166</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84979</v>
+        <v>1.88097</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.67839</v>
+        <v>16.86558</v>
       </c>
       <c r="D4" t="n">
-        <v>17.13448</v>
+        <v>16.75223</v>
       </c>
       <c r="E4" t="n">
-        <v>16.81988</v>
+        <v>16.83465</v>
       </c>
       <c r="F4" t="n">
-        <v>42.48974</v>
+        <v>43.08264</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0507</v>
+        <v>0.05195</v>
       </c>
       <c r="H4" t="n">
-        <v>1.833</v>
+        <v>1.86348</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.16631</v>
+        <v>16.97787</v>
       </c>
       <c r="D6" t="n">
-        <v>16.31644</v>
+        <v>16.32384</v>
       </c>
       <c r="E6" t="n">
-        <v>16.76252</v>
+        <v>16.66815</v>
       </c>
       <c r="F6" t="n">
-        <v>21.85736</v>
+        <v>22.22787</v>
       </c>
       <c r="G6" t="n">
-        <v>34.3729</v>
+        <v>34.31295</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.15997</v>
+        <v>16.97347</v>
       </c>
       <c r="D7" t="n">
-        <v>15.97123</v>
+        <v>16.21037</v>
       </c>
       <c r="E7" t="n">
-        <v>16.741</v>
+        <v>16.73984</v>
       </c>
       <c r="F7" t="n">
-        <v>22.19567</v>
+        <v>22.25228</v>
       </c>
       <c r="G7" t="n">
-        <v>34.73567</v>
+        <v>34.67842</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.89563</v>
+        <v>16.7494</v>
       </c>
       <c r="D8" t="n">
-        <v>16.45471</v>
+        <v>16.33365</v>
       </c>
       <c r="E8" t="n">
-        <v>16.51943</v>
+        <v>16.73685</v>
       </c>
       <c r="F8" t="n">
-        <v>21.84906</v>
+        <v>21.92164</v>
       </c>
       <c r="G8" t="n">
-        <v>34.30812</v>
+        <v>34.87486</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.62405</v>
+        <v>0.6096</v>
       </c>
       <c r="D10" t="n">
-        <v>1.14052</v>
+        <v>1.12784</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61991</v>
+        <v>0.61943</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10143</v>
+        <v>1.14638</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59985</v>
+        <v>0.6206199999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11021</v>
+        <v>1.11835</v>
       </c>
     </row>
   </sheetData>
